--- a/Team-Data/2012-13/1-1-2012-13.xlsx
+++ b/Team-Data/2012-13/1-1-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,46 +728,46 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>0.667</v>
+        <v>0.655</v>
       </c>
       <c r="H2" t="n">
         <v>48.7</v>
       </c>
       <c r="I2" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J2" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="K2" t="n">
-        <v>0.458</v>
+        <v>0.456</v>
       </c>
       <c r="L2" t="n">
         <v>8.9</v>
       </c>
       <c r="M2" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="N2" t="n">
-        <v>0.38</v>
+        <v>0.379</v>
       </c>
       <c r="O2" t="n">
-        <v>13.6</v>
+        <v>13.9</v>
       </c>
       <c r="P2" t="n">
-        <v>19.2</v>
+        <v>19.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.708</v>
+        <v>0.711</v>
       </c>
       <c r="R2" t="n">
         <v>10.1</v>
@@ -712,10 +779,10 @@
         <v>40.9</v>
       </c>
       <c r="U2" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="V2" t="n">
-        <v>14.4</v>
+        <v>14.7</v>
       </c>
       <c r="W2" t="n">
         <v>8.9</v>
@@ -727,25 +794,25 @@
         <v>4.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="AA2" t="n">
         <v>19.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>97.90000000000001</v>
+        <v>98</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
       </c>
       <c r="AF2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG2" t="n">
         <v>8</v>
@@ -763,19 +830,19 @@
         <v>7</v>
       </c>
       <c r="AL2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM2" t="n">
         <v>5</v>
       </c>
       <c r="AN2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO2" t="n">
         <v>28</v>
       </c>
       <c r="AP2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ2" t="n">
         <v>28</v>
@@ -790,16 +857,16 @@
         <v>23</v>
       </c>
       <c r="AU2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AW2" t="n">
         <v>4</v>
       </c>
       <c r="AX2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY2" t="n">
         <v>8</v>
@@ -808,7 +875,7 @@
         <v>1</v>
       </c>
       <c r="BA2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -921,16 +988,16 @@
         <v>-2.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AE3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG3" t="n">
         <v>19</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>20</v>
       </c>
       <c r="AH3" t="n">
         <v>1</v>
@@ -951,10 +1018,10 @@
         <v>28</v>
       </c>
       <c r="AN3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO3" t="n">
         <v>17</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>15</v>
       </c>
       <c r="AP3" t="n">
         <v>22</v>
@@ -975,7 +1042,7 @@
         <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
         <v>8</v>
@@ -990,7 +1057,7 @@
         <v>23</v>
       </c>
       <c r="BA3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB3" t="n">
         <v>17</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-0.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE4" t="n">
         <v>12</v>
@@ -1115,16 +1182,16 @@
         <v>16</v>
       </c>
       <c r="AH4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI4" t="n">
         <v>28</v>
       </c>
       <c r="AJ4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
         <v>12</v>
@@ -1148,13 +1215,13 @@
         <v>10</v>
       </c>
       <c r="AS4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT4" t="n">
         <v>22</v>
       </c>
       <c r="AU4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV4" t="n">
         <v>8</v>
@@ -1163,7 +1230,7 @@
         <v>25</v>
       </c>
       <c r="AX4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY4" t="n">
         <v>5</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-8.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE5" t="n">
         <v>27</v>
@@ -1327,7 +1394,7 @@
         <v>20</v>
       </c>
       <c r="AR5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS5" t="n">
         <v>20</v>
@@ -1342,16 +1409,16 @@
         <v>7</v>
       </c>
       <c r="AW5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY5" t="n">
         <v>30</v>
       </c>
       <c r="AZ5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA5" t="n">
         <v>6</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>0.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
         <v>12</v>
@@ -1521,10 +1588,10 @@
         <v>10</v>
       </c>
       <c r="AV6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX6" t="n">
         <v>17</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -1649,19 +1716,19 @@
         <v>-5.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
         <v>28</v>
       </c>
       <c r="AF7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG7" t="n">
         <v>29</v>
       </c>
       <c r="AH7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
         <v>24</v>
@@ -1685,7 +1752,7 @@
         <v>24</v>
       </c>
       <c r="AP7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ7" t="n">
         <v>23</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -1753,46 +1820,46 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8" t="n">
         <v>19</v>
       </c>
       <c r="G8" t="n">
-        <v>0.406</v>
+        <v>0.387</v>
       </c>
       <c r="H8" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="I8" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J8" t="n">
-        <v>83.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L8" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M8" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0.355</v>
+        <v>0.352</v>
       </c>
       <c r="O8" t="n">
-        <v>16.9</v>
+        <v>17.1</v>
       </c>
       <c r="P8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.78</v>
+        <v>0.784</v>
       </c>
       <c r="R8" t="n">
         <v>9.5</v>
@@ -1804,34 +1871,34 @@
         <v>41.3</v>
       </c>
       <c r="U8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V8" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W8" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X8" t="n">
         <v>5.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>98.5</v>
+        <v>98.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>-4.4</v>
+        <v>-4.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE8" t="n">
         <v>21</v>
@@ -1843,34 +1910,34 @@
         <v>21</v>
       </c>
       <c r="AH8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK8" t="n">
         <v>14</v>
       </c>
       <c r="AL8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM8" t="n">
         <v>14</v>
       </c>
       <c r="AN8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR8" t="n">
         <v>27</v>
@@ -1879,28 +1946,28 @@
         <v>11</v>
       </c>
       <c r="AT8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV8" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AW8" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AX8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY8" t="n">
         <v>7</v>
       </c>
       <c r="AZ8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB8" t="n">
         <v>11</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -1935,88 +2002,88 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F9" t="n">
         <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>0.545</v>
+        <v>0.531</v>
       </c>
       <c r="H9" t="n">
         <v>48.3</v>
       </c>
       <c r="I9" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="J9" t="n">
         <v>84.40000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.465</v>
+        <v>0.466</v>
       </c>
       <c r="L9" t="n">
         <v>6.2</v>
       </c>
       <c r="M9" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="N9" t="n">
-        <v>0.33</v>
+        <v>0.331</v>
       </c>
       <c r="O9" t="n">
-        <v>16.9</v>
+        <v>17.1</v>
       </c>
       <c r="P9" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.681</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="R9" t="n">
         <v>13.9</v>
       </c>
       <c r="S9" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T9" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
       <c r="U9" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="V9" t="n">
         <v>15.6</v>
       </c>
       <c r="W9" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X9" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="Y9" t="n">
         <v>6.7</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>101.6</v>
+        <v>101.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF9" t="n">
         <v>15</v>
@@ -2025,7 +2092,7 @@
         <v>13</v>
       </c>
       <c r="AH9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI9" t="n">
         <v>2</v>
@@ -2046,7 +2113,7 @@
         <v>28</v>
       </c>
       <c r="AO9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AP9" t="n">
         <v>7</v>
@@ -2058,7 +2125,7 @@
         <v>1</v>
       </c>
       <c r="AS9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT9" t="n">
         <v>1</v>
@@ -2067,28 +2134,28 @@
         <v>5</v>
       </c>
       <c r="AV9" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AW9" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AX9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY9" t="n">
         <v>27</v>
       </c>
       <c r="AZ9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB9" t="n">
         <v>8</v>
       </c>
       <c r="BC9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -2117,37 +2184,37 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
         <v>22</v>
       </c>
       <c r="G10" t="n">
-        <v>0.353</v>
+        <v>0.333</v>
       </c>
       <c r="H10" t="n">
         <v>48.6</v>
       </c>
       <c r="I10" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J10" t="n">
-        <v>81</v>
+        <v>81.2</v>
       </c>
       <c r="K10" t="n">
-        <v>0.442</v>
+        <v>0.44</v>
       </c>
       <c r="L10" t="n">
         <v>6.3</v>
       </c>
       <c r="M10" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0.382</v>
+        <v>0.381</v>
       </c>
       <c r="O10" t="n">
         <v>17.2</v>
@@ -2156,7 +2223,7 @@
         <v>23.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.722</v>
+        <v>0.72</v>
       </c>
       <c r="R10" t="n">
         <v>12.5</v>
@@ -2165,58 +2232,58 @@
         <v>30.9</v>
       </c>
       <c r="T10" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
       <c r="U10" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V10" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
         <v>6</v>
       </c>
       <c r="X10" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y10" t="n">
         <v>5.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="AA10" t="n">
         <v>20.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>95.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.5</v>
+        <v>-1.7</v>
       </c>
       <c r="AD10" t="n">
         <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF10" t="n">
         <v>26</v>
       </c>
       <c r="AG10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI10" t="n">
         <v>21</v>
       </c>
       <c r="AJ10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL10" t="n">
         <v>22</v>
@@ -2234,7 +2301,7 @@
         <v>9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR10" t="n">
         <v>7</v>
@@ -2249,13 +2316,13 @@
         <v>24</v>
       </c>
       <c r="AV10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW10" t="n">
         <v>29</v>
       </c>
       <c r="AX10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY10" t="n">
         <v>22</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -2377,16 +2444,16 @@
         <v>2.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE11" t="n">
         <v>4</v>
       </c>
       <c r="AF11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH11" t="n">
         <v>7</v>
@@ -2404,7 +2471,7 @@
         <v>8</v>
       </c>
       <c r="AM11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AN11" t="n">
         <v>5</v>
@@ -2413,7 +2480,7 @@
         <v>13</v>
       </c>
       <c r="AP11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ11" t="n">
         <v>6</v>
@@ -2452,7 +2519,7 @@
         <v>9</v>
       </c>
       <c r="BC11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -2559,10 +2626,10 @@
         <v>2</v>
       </c>
       <c r="AD12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE12" t="n">
         <v>10</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>11</v>
       </c>
       <c r="AF12" t="n">
         <v>13</v>
@@ -2571,7 +2638,7 @@
         <v>12</v>
       </c>
       <c r="AH12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI12" t="n">
         <v>7</v>
@@ -2580,7 +2647,7 @@
         <v>7</v>
       </c>
       <c r="AK12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL12" t="n">
         <v>2</v>
@@ -2589,7 +2656,7 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO12" t="n">
         <v>3</v>
@@ -2598,7 +2665,7 @@
         <v>4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR12" t="n">
         <v>21</v>
@@ -2634,7 +2701,7 @@
         <v>2</v>
       </c>
       <c r="BC12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>1.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE13" t="n">
         <v>9</v>
@@ -2753,7 +2820,7 @@
         <v>9</v>
       </c>
       <c r="AH13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI13" t="n">
         <v>29</v>
@@ -2765,16 +2832,16 @@
         <v>27</v>
       </c>
       <c r="AL13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM13" t="n">
         <v>18</v>
       </c>
       <c r="AN13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP13" t="n">
         <v>11</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -2845,58 +2912,58 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E14" t="n">
         <v>25</v>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
-        <v>0.781</v>
+        <v>0.806</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
       </c>
       <c r="I14" t="n">
-        <v>38.5</v>
+        <v>38.8</v>
       </c>
       <c r="J14" t="n">
         <v>80.7</v>
       </c>
       <c r="K14" t="n">
-        <v>0.478</v>
+        <v>0.481</v>
       </c>
       <c r="L14" t="n">
         <v>7.1</v>
       </c>
       <c r="M14" t="n">
-        <v>20.4</v>
+        <v>20.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.347</v>
+        <v>0.355</v>
       </c>
       <c r="O14" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P14" t="n">
-        <v>24.6</v>
+        <v>24.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.711</v>
+        <v>0.721</v>
       </c>
       <c r="R14" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S14" t="n">
         <v>30.5</v>
       </c>
       <c r="T14" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U14" t="n">
-        <v>23.4</v>
+        <v>23.7</v>
       </c>
       <c r="V14" t="n">
         <v>14.5</v>
@@ -2911,49 +2978,49 @@
         <v>4.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>101.6</v>
+        <v>102.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.300000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
         <v>30</v>
       </c>
       <c r="AI14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ14" t="n">
         <v>23</v>
       </c>
       <c r="AK14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL14" t="n">
         <v>13</v>
       </c>
       <c r="AM14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AO14" t="n">
         <v>9</v>
@@ -2962,10 +3029,10 @@
         <v>8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS14" t="n">
         <v>18</v>
@@ -2974,10 +3041,10 @@
         <v>18</v>
       </c>
       <c r="AU14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -2989,13 +3056,13 @@
         <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BA14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E15" t="n">
         <v>15</v>
       </c>
       <c r="F15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G15" t="n">
-        <v>0.484</v>
+        <v>0.5</v>
       </c>
       <c r="H15" t="n">
         <v>48.2</v>
@@ -3045,73 +3112,73 @@
         <v>36.8</v>
       </c>
       <c r="J15" t="n">
-        <v>81.2</v>
+        <v>80.8</v>
       </c>
       <c r="K15" t="n">
-        <v>0.453</v>
+        <v>0.455</v>
       </c>
       <c r="L15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="M15" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0.358</v>
+        <v>0.364</v>
       </c>
       <c r="O15" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="P15" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="R15" t="n">
         <v>13.1</v>
       </c>
       <c r="S15" t="n">
-        <v>33</v>
+        <v>32.8</v>
       </c>
       <c r="T15" t="n">
-        <v>46.1</v>
+        <v>45.9</v>
       </c>
       <c r="U15" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="V15" t="n">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
       <c r="W15" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X15" t="n">
         <v>5.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.8</v>
+        <v>103</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AE15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AG15" t="n">
         <v>17</v>
@@ -3120,22 +3187,22 @@
         <v>28</v>
       </c>
       <c r="AI15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM15" t="n">
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AO15" t="n">
         <v>2</v>
@@ -3150,16 +3217,16 @@
         <v>5</v>
       </c>
       <c r="AS15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU15" t="n">
         <v>19</v>
       </c>
       <c r="AV15" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AW15" t="n">
         <v>20</v>
@@ -3168,10 +3235,10 @@
         <v>8</v>
       </c>
       <c r="AY15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA15" t="n">
         <v>1</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -3287,22 +3354,22 @@
         <v>4.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF16" t="n">
         <v>5</v>
       </c>
       <c r="AG16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH16" t="n">
         <v>18</v>
       </c>
       <c r="AI16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ16" t="n">
         <v>9</v>
@@ -3317,10 +3384,10 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP16" t="n">
         <v>21</v>
@@ -3332,13 +3399,13 @@
         <v>2</v>
       </c>
       <c r="AS16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT16" t="n">
         <v>12</v>
       </c>
       <c r="AU16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV16" t="n">
         <v>18</v>
@@ -3353,7 +3420,7 @@
         <v>24</v>
       </c>
       <c r="AZ16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA16" t="n">
         <v>11</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>4.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE17" t="n">
         <v>4</v>
@@ -3484,7 +3551,7 @@
         <v>19</v>
       </c>
       <c r="AI17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-0.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
         <v>12</v>
@@ -3702,7 +3769,7 @@
         <v>13</v>
       </c>
       <c r="AU18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV18" t="n">
         <v>6</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -3836,13 +3903,13 @@
         <v>30</v>
       </c>
       <c r="AE19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF19" t="n">
         <v>9</v>
       </c>
       <c r="AG19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH19" t="n">
         <v>26</v>
@@ -3872,7 +3939,7 @@
         <v>5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR19" t="n">
         <v>3</v>
@@ -3881,13 +3948,13 @@
         <v>8</v>
       </c>
       <c r="AT19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU19" t="n">
         <v>14</v>
       </c>
       <c r="AV19" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AW19" t="n">
         <v>15</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -3937,64 +4004,64 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E20" t="n">
         <v>7</v>
       </c>
       <c r="F20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G20" t="n">
-        <v>0.226</v>
+        <v>0.233</v>
       </c>
       <c r="H20" t="n">
         <v>48.5</v>
       </c>
       <c r="I20" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="J20" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="K20" t="n">
         <v>0.441</v>
       </c>
       <c r="L20" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M20" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0.38</v>
+        <v>0.376</v>
       </c>
       <c r="O20" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="P20" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="R20" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S20" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T20" t="n">
-        <v>40.7</v>
+        <v>40.5</v>
       </c>
       <c r="U20" t="n">
         <v>20.9</v>
       </c>
       <c r="V20" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W20" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="X20" t="n">
         <v>5.5</v>
@@ -4003,73 +4070,73 @@
         <v>6.9</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>91.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>-6</v>
+        <v>-5.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AE20" t="n">
         <v>28</v>
       </c>
       <c r="AF20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG20" t="n">
         <v>28</v>
       </c>
       <c r="AH20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI20" t="n">
         <v>27</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AM20" t="n">
         <v>21</v>
       </c>
       <c r="AN20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP20" t="n">
         <v>28</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR20" t="n">
         <v>20</v>
       </c>
       <c r="AS20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW20" t="n">
         <v>28</v>
@@ -4081,10 +4148,10 @@
         <v>28</v>
       </c>
       <c r="AZ20" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB20" t="n">
         <v>29</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E21" t="n">
         <v>21</v>
       </c>
       <c r="F21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G21" t="n">
-        <v>0.677</v>
+        <v>0.7</v>
       </c>
       <c r="H21" t="n">
         <v>48.2</v>
@@ -4146,31 +4213,31 @@
         <v>11.3</v>
       </c>
       <c r="M21" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0.388</v>
+        <v>0.393</v>
       </c>
       <c r="O21" t="n">
         <v>15.9</v>
       </c>
       <c r="P21" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="Q21" t="n">
         <v>0.75</v>
       </c>
       <c r="R21" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S21" t="n">
-        <v>29.2</v>
+        <v>29.4</v>
       </c>
       <c r="T21" t="n">
-        <v>39.7</v>
+        <v>39.8</v>
       </c>
       <c r="U21" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V21" t="n">
         <v>11</v>
@@ -4179,34 +4246,34 @@
         <v>8.699999999999999</v>
       </c>
       <c r="X21" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Z21" t="n">
         <v>18.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>102.2</v>
+        <v>102.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AE21" t="n">
         <v>4</v>
       </c>
       <c r="AF21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH21" t="n">
         <v>28</v>
@@ -4233,22 +4300,22 @@
         <v>23</v>
       </c>
       <c r="AP21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ21" t="n">
         <v>18</v>
       </c>
       <c r="AR21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT21" t="n">
         <v>28</v>
       </c>
       <c r="AU21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
@@ -4269,7 +4336,7 @@
         <v>20</v>
       </c>
       <c r="BB21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC21" t="n">
         <v>4</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -4388,7 +4455,7 @@
         <v>1</v>
       </c>
       <c r="AG22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="n">
         <v>11</v>
@@ -4400,7 +4467,7 @@
         <v>29</v>
       </c>
       <c r="AK22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL22" t="n">
         <v>11</v>
@@ -4424,7 +4491,7 @@
         <v>22</v>
       </c>
       <c r="AS22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
         <v>7</v>
@@ -4433,7 +4500,7 @@
         <v>13</v>
       </c>
       <c r="AV22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW22" t="n">
         <v>16</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -4561,22 +4628,22 @@
         <v>-2.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF23" t="n">
         <v>21</v>
       </c>
       <c r="AG23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH23" t="n">
         <v>22</v>
       </c>
-      <c r="AH23" t="n">
-        <v>21</v>
-      </c>
       <c r="AI23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ23" t="n">
         <v>17</v>
@@ -4624,16 +4691,16 @@
         <v>25</v>
       </c>
       <c r="AY23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>10</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>9</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC23" t="n">
         <v>22</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -4665,34 +4732,34 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F24" t="n">
         <v>17</v>
       </c>
       <c r="G24" t="n">
-        <v>0.469</v>
+        <v>0.452</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>36.9</v>
+        <v>36.7</v>
       </c>
       <c r="J24" t="n">
-        <v>84</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L24" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M24" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="N24" t="n">
         <v>0.359</v>
@@ -4704,19 +4771,19 @@
         <v>18.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.724</v>
+        <v>0.727</v>
       </c>
       <c r="R24" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="S24" t="n">
-        <v>30.5</v>
+        <v>30</v>
       </c>
       <c r="T24" t="n">
-        <v>41.8</v>
+        <v>41.5</v>
       </c>
       <c r="U24" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="V24" t="n">
         <v>12.4</v>
@@ -4725,55 +4792,55 @@
         <v>7.7</v>
       </c>
       <c r="X24" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y24" t="n">
         <v>4.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AA24" t="n">
         <v>17.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>93.5</v>
+        <v>93.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>-2.4</v>
+        <v>-2.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AF24" t="n">
         <v>19</v>
       </c>
       <c r="AG24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AH24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ24" t="n">
         <v>5</v>
       </c>
       <c r="AK24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL24" t="n">
         <v>18</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>17</v>
       </c>
       <c r="AM24" t="n">
         <v>22</v>
       </c>
       <c r="AN24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO24" t="n">
         <v>29</v>
@@ -4782,10 +4849,10 @@
         <v>29</v>
       </c>
       <c r="AQ24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS24" t="n">
         <v>19</v>
@@ -4794,7 +4861,7 @@
         <v>19</v>
       </c>
       <c r="AU24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV24" t="n">
         <v>2</v>
@@ -4803,10 +4870,10 @@
         <v>19</v>
       </c>
       <c r="AX24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ24" t="n">
         <v>8</v>
@@ -4815,7 +4882,7 @@
         <v>29</v>
       </c>
       <c r="BB24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC24" t="n">
         <v>21</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -4925,16 +4992,16 @@
         <v>-4.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF25" t="n">
         <v>25</v>
       </c>
       <c r="AG25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH25" t="n">
         <v>16</v>
@@ -4949,7 +5016,7 @@
         <v>12</v>
       </c>
       <c r="AL25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM25" t="n">
         <v>17</v>
@@ -4958,10 +5025,10 @@
         <v>26</v>
       </c>
       <c r="AO25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ25" t="n">
         <v>17</v>
@@ -4982,7 +5049,7 @@
         <v>4</v>
       </c>
       <c r="AW25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX25" t="n">
         <v>9</v>
@@ -4994,7 +5061,7 @@
         <v>21</v>
       </c>
       <c r="BA25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB25" t="n">
         <v>13</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -5029,106 +5096,106 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F26" t="n">
         <v>14</v>
       </c>
       <c r="G26" t="n">
-        <v>0.533</v>
+        <v>0.517</v>
       </c>
       <c r="H26" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="I26" t="n">
-        <v>36.4</v>
+        <v>36.2</v>
       </c>
       <c r="J26" t="n">
         <v>83</v>
       </c>
       <c r="K26" t="n">
-        <v>0.438</v>
+        <v>0.436</v>
       </c>
       <c r="L26" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M26" t="n">
-        <v>23.7</v>
+        <v>23.4</v>
       </c>
       <c r="N26" t="n">
         <v>0.337</v>
       </c>
       <c r="O26" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="P26" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.766</v>
+        <v>0.769</v>
       </c>
       <c r="R26" t="n">
         <v>12</v>
       </c>
       <c r="S26" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T26" t="n">
-        <v>41.5</v>
+        <v>41.3</v>
       </c>
       <c r="U26" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V26" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W26" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X26" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="Y26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AA26" t="n">
         <v>19.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.2</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>-1.9</v>
+        <v>-2.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE26" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AF26" t="n">
         <v>13</v>
       </c>
       <c r="AG26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH26" t="n">
         <v>5</v>
       </c>
       <c r="AI26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ26" t="n">
         <v>13</v>
       </c>
       <c r="AK26" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL26" t="n">
         <v>7</v>
@@ -5143,22 +5210,22 @@
         <v>21</v>
       </c>
       <c r="AP26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ26" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR26" t="n">
         <v>11</v>
       </c>
       <c r="AS26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV26" t="n">
         <v>14</v>
@@ -5167,16 +5234,16 @@
         <v>11</v>
       </c>
       <c r="AX26" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AY26" t="n">
         <v>4</v>
       </c>
       <c r="AZ26" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB26" t="n">
         <v>14</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E27" t="n">
         <v>11</v>
       </c>
       <c r="F27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G27" t="n">
-        <v>0.355</v>
+        <v>0.367</v>
       </c>
       <c r="H27" t="n">
         <v>48.3</v>
@@ -5229,19 +5296,19 @@
         <v>36.5</v>
       </c>
       <c r="J27" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="K27" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L27" t="n">
         <v>7</v>
       </c>
       <c r="M27" t="n">
-        <v>19.4</v>
+        <v>19.1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.363</v>
+        <v>0.364</v>
       </c>
       <c r="O27" t="n">
         <v>16.8</v>
@@ -5253,13 +5320,13 @@
         <v>0.771</v>
       </c>
       <c r="R27" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S27" t="n">
-        <v>28.8</v>
+        <v>29.1</v>
       </c>
       <c r="T27" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U27" t="n">
         <v>19.8</v>
@@ -5268,19 +5335,19 @@
         <v>14.5</v>
       </c>
       <c r="W27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X27" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="Z27" t="n">
         <v>21.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB27" t="n">
         <v>96.8</v>
@@ -5289,13 +5356,13 @@
         <v>-5</v>
       </c>
       <c r="AD27" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AE27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF27" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG27" t="n">
         <v>23</v>
@@ -5307,10 +5374,10 @@
         <v>17</v>
       </c>
       <c r="AJ27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AK27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL27" t="n">
         <v>14</v>
@@ -5319,7 +5386,7 @@
         <v>16</v>
       </c>
       <c r="AN27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO27" t="n">
         <v>19</v>
@@ -5334,16 +5401,16 @@
         <v>16</v>
       </c>
       <c r="AS27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU27" t="n">
         <v>28</v>
       </c>
       <c r="AV27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW27" t="n">
         <v>9</v>
@@ -5355,10 +5422,10 @@
         <v>26</v>
       </c>
       <c r="AZ27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA27" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BB27" t="n">
         <v>15</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>9.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5507,7 +5574,7 @@
         <v>18</v>
       </c>
       <c r="AP28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ28" t="n">
         <v>5</v>
@@ -5531,16 +5598,16 @@
         <v>6</v>
       </c>
       <c r="AX28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ28" t="n">
         <v>2</v>
       </c>
       <c r="BA28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB28" t="n">
         <v>3</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -5653,16 +5720,16 @@
         <v>-3.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF29" t="n">
         <v>24</v>
       </c>
-      <c r="AF29" t="n">
-        <v>23</v>
-      </c>
       <c r="AG29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH29" t="n">
         <v>2</v>
@@ -5692,28 +5759,28 @@
         <v>13</v>
       </c>
       <c r="AQ29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AR29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT29" t="n">
         <v>26</v>
       </c>
       <c r="AU29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV29" t="n">
         <v>3</v>
       </c>
       <c r="AW29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY29" t="n">
         <v>19</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -5835,10 +5902,10 @@
         <v>-1.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF30" t="n">
         <v>19</v>
@@ -5874,7 +5941,7 @@
         <v>6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR30" t="n">
         <v>6</v>
@@ -5892,7 +5959,7 @@
         <v>17</v>
       </c>
       <c r="AW30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX30" t="n">
         <v>7</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
@@ -5939,49 +6006,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E31" t="n">
         <v>4</v>
       </c>
       <c r="F31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G31" t="n">
-        <v>0.138</v>
+        <v>0.143</v>
       </c>
       <c r="H31" t="n">
         <v>48.9</v>
       </c>
       <c r="I31" t="n">
-        <v>33.7</v>
+        <v>33.8</v>
       </c>
       <c r="J31" t="n">
-        <v>83.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="K31" t="n">
         <v>0.406</v>
       </c>
       <c r="L31" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M31" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="N31" t="n">
-        <v>0.314</v>
+        <v>0.311</v>
       </c>
       <c r="O31" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="P31" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.755</v>
+        <v>0.754</v>
       </c>
       <c r="R31" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S31" t="n">
         <v>32.3</v>
@@ -5990,34 +6057,34 @@
         <v>43.9</v>
       </c>
       <c r="U31" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V31" t="n">
         <v>15.3</v>
       </c>
       <c r="W31" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="X31" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>88.90000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7.9</v>
+        <v>-7.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE31" t="n">
         <v>30</v>
@@ -6035,16 +6102,16 @@
         <v>30</v>
       </c>
       <c r="AJ31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK31" t="n">
         <v>30</v>
       </c>
       <c r="AL31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN31" t="n">
         <v>29</v>
@@ -6062,19 +6129,19 @@
         <v>15</v>
       </c>
       <c r="AS31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT31" t="n">
         <v>6</v>
       </c>
       <c r="AU31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV31" t="n">
         <v>20</v>
       </c>
       <c r="AW31" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AX31" t="n">
         <v>22</v>
@@ -6086,7 +6153,7 @@
         <v>22</v>
       </c>
       <c r="BA31" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BB31" t="n">
         <v>30</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-1-2012-13</t>
+          <t>2013-01-01</t>
         </is>
       </c>
     </row>
